--- a/artfynd/A 13181-2025 artfynd.xlsx
+++ b/artfynd/A 13181-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122715474</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>122715470</v>
       </c>
       <c r="B4" t="n">
-        <v>57499</v>
+        <v>57502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
